--- a/ANF.xlsx
+++ b/ANF.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B8DC616-2B13-43D5-B93D-C51990484B64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85674FBA-144D-4716-9359-FFE6EE7DE217}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{5386E427-DDBF-4556-BEE6-790EAB42F0A7}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{5386E427-DDBF-4556-BEE6-790EAB42F0A7}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -1075,13 +1075,19 @@
     <numFmt numFmtId="170" formatCode="#,##0;\(#,##0\)"/>
     <numFmt numFmtId="171" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1419,132 +1425,135 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="169" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="3" fillId="2" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="16" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="167" fontId="3" fillId="2" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="17" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="8" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="169" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="170" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="2" fillId="2" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="167" fontId="2" fillId="2" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="16" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="7" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1886,7 +1895,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAEC40C0-B144-4655-82AF-8123A26C51E9}">
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="2" customWidth="1"/>
@@ -1910,7 +1919,7 @@
         <v>2</v>
       </c>
       <c r="I2" s="2">
-        <v>83.06</v>
+        <v>148.80000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -1918,10 +1927,10 @@
         <v>3</v>
       </c>
       <c r="I3" s="3">
-        <v>44.969000000000001</v>
-      </c>
-      <c r="J3" s="82" t="s">
-        <v>315</v>
+        <v>43.767000000000003</v>
+      </c>
+      <c r="J3" s="83" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -1936,7 +1945,7 @@
       </c>
       <c r="I4" s="5">
         <f>I2*I3</f>
-        <v>3735.1251400000001</v>
+        <v>6512.5296000000008</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -1950,11 +1959,11 @@
         <v>5</v>
       </c>
       <c r="I5" s="5">
-        <f>594.08+25.144</f>
-        <v>619.22400000000005</v>
-      </c>
-      <c r="J5" s="82" t="s">
-        <v>315</v>
+        <f>627.716+10.283</f>
+        <v>637.99900000000002</v>
+      </c>
+      <c r="J5" s="83" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -1964,8 +1973,8 @@
       <c r="I6" s="5">
         <v>0</v>
       </c>
-      <c r="J6" s="82" t="s">
-        <v>315</v>
+      <c r="J6" s="83" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -1974,7 +1983,7 @@
       </c>
       <c r="I7" s="5">
         <f>I4+I6-I5</f>
-        <v>3115.9011399999999</v>
+        <v>5874.530600000001</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -1996,6 +2005,9 @@
       <c r="E9" s="9" t="s">
         <v>38</v>
       </c>
+      <c r="H9" s="2" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B10" s="10" t="s">
@@ -2009,6 +2021,9 @@
         <v>99</v>
       </c>
       <c r="E10" s="13"/>
+      <c r="H10" s="2" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B11" s="14" t="s">
@@ -2021,85 +2036,71 @@
         <v>100</v>
       </c>
       <c r="E11" s="16"/>
+      <c r="H11" s="2" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B12" s="17"/>
       <c r="C12" s="18"/>
       <c r="D12" s="19"/>
       <c r="E12" s="20"/>
+      <c r="H12" s="2" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
-        <v>130</v>
+        <v>122</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B18" s="2" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
-        <v>124</v>
+        <v>308</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B25" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B26" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B27" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B28" s="2" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B29" s="2" t="s">
         <v>309</v>
       </c>
     </row>
@@ -2163,16 +2164,16 @@
       <c r="N2" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="O2" s="82" t="s">
+      <c r="O2" s="78" t="s">
         <v>315</v>
       </c>
-      <c r="P2" s="82" t="s">
+      <c r="P2" s="78" t="s">
         <v>316</v>
       </c>
-      <c r="Q2" s="82" t="s">
+      <c r="Q2" s="78" t="s">
         <v>317</v>
       </c>
-      <c r="R2" s="82" t="s">
+      <c r="R2" s="78" t="s">
         <v>318</v>
       </c>
       <c r="S2" s="4"/>
@@ -2447,7 +2448,9 @@
       <c r="O8" s="3">
         <v>899.94399999999996</v>
       </c>
-      <c r="P8" s="3"/>
+      <c r="P8" s="3">
+        <v>1020.537</v>
+      </c>
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
       <c r="S8" s="3"/>
@@ -2551,7 +2554,9 @@
       <c r="O9" s="3">
         <v>167.37299999999999</v>
       </c>
-      <c r="P9" s="3"/>
+      <c r="P9" s="3">
+        <v>201.99</v>
+      </c>
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
       <c r="S9" s="3"/>
@@ -2655,7 +2660,9 @@
       <c r="O10" s="3">
         <v>46.503999999999998</v>
       </c>
-      <c r="P10" s="3"/>
+      <c r="P10" s="3">
+        <v>44.161999999999999</v>
+      </c>
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
       <c r="S10" s="3"/>
@@ -2763,7 +2770,9 @@
       <c r="O11" s="3">
         <v>564.71900000000005</v>
       </c>
-      <c r="P11" s="3"/>
+      <c r="P11" s="3">
+        <v>596.80799999999999</v>
+      </c>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
@@ -2846,52 +2855,52 @@
       <c r="B12" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C12" s="82" t="s">
+      <c r="C12" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="D12" s="82" t="s">
+      <c r="D12" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="E12" s="82" t="s">
+      <c r="E12" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="F12" s="82" t="s">
+      <c r="F12" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="G12" s="82" t="s">
+      <c r="G12" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="H12" s="82" t="s">
+      <c r="H12" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="I12" s="82" t="s">
+      <c r="I12" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="J12" s="82" t="s">
+      <c r="J12" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="K12" s="82" t="s">
+      <c r="K12" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="L12" s="82" t="s">
+      <c r="L12" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="M12" s="82" t="s">
+      <c r="M12" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="N12" s="82" t="s">
+      <c r="N12" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="O12" s="82" t="s">
+      <c r="O12" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="P12" s="82" t="s">
+      <c r="P12" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="Q12" s="82" t="s">
+      <c r="Q12" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="R12" s="82" t="s">
+      <c r="R12" s="78" t="s">
         <v>319</v>
       </c>
       <c r="S12" s="3"/>
@@ -2967,52 +2976,52 @@
       <c r="B13" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="C13" s="82" t="s">
+      <c r="C13" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="D13" s="82" t="s">
+      <c r="D13" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="E13" s="82" t="s">
+      <c r="E13" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="F13" s="82" t="s">
+      <c r="F13" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="G13" s="82" t="s">
+      <c r="G13" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="H13" s="82" t="s">
+      <c r="H13" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="I13" s="82" t="s">
+      <c r="I13" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="J13" s="82" t="s">
+      <c r="J13" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="K13" s="82" t="s">
+      <c r="K13" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="L13" s="82" t="s">
+      <c r="L13" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="M13" s="82" t="s">
+      <c r="M13" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="N13" s="82" t="s">
+      <c r="N13" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="O13" s="82" t="s">
+      <c r="O13" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="P13" s="82" t="s">
+      <c r="P13" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="Q13" s="82" t="s">
+      <c r="Q13" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="R13" s="82" t="s">
+      <c r="R13" s="78" t="s">
         <v>319</v>
       </c>
       <c r="S13" s="3"/>
@@ -3125,7 +3134,9 @@
       <c r="O14" s="3">
         <v>549.10199999999998</v>
       </c>
-      <c r="P14" s="3"/>
+      <c r="P14" s="3">
+        <v>669.88099999999997</v>
+      </c>
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
       <c r="S14" s="3"/>
@@ -3208,52 +3219,52 @@
       <c r="B15" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C15" s="82" t="s">
+      <c r="C15" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="D15" s="82" t="s">
+      <c r="D15" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="E15" s="82" t="s">
+      <c r="E15" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="F15" s="82" t="s">
+      <c r="F15" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="G15" s="82" t="s">
+      <c r="G15" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="H15" s="82" t="s">
+      <c r="H15" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="I15" s="82" t="s">
+      <c r="I15" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="J15" s="82" t="s">
+      <c r="J15" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="K15" s="82" t="s">
+      <c r="K15" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="L15" s="82" t="s">
+      <c r="L15" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="M15" s="82" t="s">
+      <c r="M15" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="N15" s="82" t="s">
+      <c r="N15" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="O15" s="82" t="s">
+      <c r="O15" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="P15" s="82" t="s">
+      <c r="P15" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="Q15" s="82" t="s">
+      <c r="Q15" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="R15" s="82" t="s">
+      <c r="R15" s="78" t="s">
         <v>319</v>
       </c>
       <c r="S15" s="3"/>
@@ -3329,52 +3340,52 @@
       <c r="B16" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="C16" s="82" t="s">
+      <c r="C16" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="D16" s="82" t="s">
+      <c r="D16" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="E16" s="82" t="s">
+      <c r="E16" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="F16" s="82" t="s">
+      <c r="F16" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="G16" s="82" t="s">
+      <c r="G16" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="H16" s="82" t="s">
+      <c r="H16" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="I16" s="82" t="s">
+      <c r="I16" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="J16" s="82" t="s">
+      <c r="J16" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="K16" s="82" t="s">
+      <c r="K16" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="L16" s="82" t="s">
+      <c r="L16" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="M16" s="82" t="s">
+      <c r="M16" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="N16" s="82" t="s">
+      <c r="N16" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="O16" s="82" t="s">
+      <c r="O16" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="P16" s="82" t="s">
+      <c r="P16" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="Q16" s="82" t="s">
+      <c r="Q16" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="R16" s="82" t="s">
+      <c r="R16" s="78" t="s">
         <v>319</v>
       </c>
       <c r="S16" s="3"/>
@@ -3492,7 +3503,9 @@
       <c r="O17" s="24">
         <v>1113.8209999999999</v>
       </c>
-      <c r="P17" s="24"/>
+      <c r="P17" s="24">
+        <v>1266.6890000000001</v>
+      </c>
       <c r="Q17" s="24"/>
       <c r="R17" s="24"/>
       <c r="S17" s="3"/>
@@ -3617,7 +3630,9 @@
       <c r="O18" s="3">
         <v>413.83800000000002</v>
       </c>
-      <c r="P18" s="3"/>
+      <c r="P18" s="3">
+        <v>366.10899999999998</v>
+      </c>
       <c r="Q18" s="3"/>
       <c r="R18" s="3"/>
       <c r="S18" s="3"/>
@@ -3720,7 +3735,7 @@
         <v>677.45699999999999</v>
       </c>
       <c r="H19" s="3">
-        <f t="shared" ref="H19:O19" si="3">H17-H18</f>
+        <f t="shared" ref="H19:P19" si="3">H17-H18</f>
         <v>736.26200000000017</v>
       </c>
       <c r="I19" s="3">
@@ -3748,7 +3763,10 @@
         <f t="shared" si="3"/>
         <v>699.98299999999995</v>
       </c>
-      <c r="P19" s="3"/>
+      <c r="P19" s="3">
+        <f t="shared" si="3"/>
+        <v>900.58000000000015</v>
+      </c>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
@@ -3875,7 +3893,9 @@
       <c r="O20" s="3">
         <v>431.19499999999999</v>
       </c>
-      <c r="P20" s="3"/>
+      <c r="P20" s="3">
+        <v>444.04199999999997</v>
+      </c>
       <c r="Q20" s="3"/>
       <c r="R20" s="3"/>
       <c r="S20" s="3"/>
@@ -3994,7 +4014,9 @@
       <c r="O21" s="3">
         <v>182.75399999999999</v>
       </c>
-      <c r="P21" s="3"/>
+      <c r="P21" s="3">
+        <v>204.78399999999999</v>
+      </c>
       <c r="Q21" s="3"/>
       <c r="R21" s="3"/>
       <c r="S21" s="3"/>
@@ -4113,7 +4135,9 @@
       <c r="O22" s="3">
         <v>2.7629999999999999</v>
       </c>
-      <c r="P22" s="3"/>
+      <c r="P22" s="3">
+        <v>0.94799999999999995</v>
+      </c>
       <c r="Q22" s="3"/>
       <c r="R22" s="3"/>
       <c r="S22" s="3"/>
@@ -4219,7 +4243,7 @@
         <v>129.84900000000002</v>
       </c>
       <c r="H23" s="3">
-        <f t="shared" ref="H23:O23" si="12">H19-H20-H21+H22</f>
+        <f t="shared" ref="H23:P23" si="12">H19-H20-H21+H22</f>
         <v>175.62500000000017</v>
       </c>
       <c r="I23" s="3">
@@ -4250,7 +4274,10 @@
         <f t="shared" si="12"/>
         <v>88.796999999999969</v>
       </c>
-      <c r="P23" s="3"/>
+      <c r="P23" s="3">
+        <f t="shared" si="12"/>
+        <v>252.7020000000002</v>
+      </c>
       <c r="Q23" s="3"/>
       <c r="R23" s="3"/>
       <c r="S23" s="3"/>
@@ -4377,7 +4404,9 @@
       <c r="O24" s="3">
         <v>0.45</v>
       </c>
-      <c r="P24" s="3"/>
+      <c r="P24" s="3">
+        <v>0.56100000000000005</v>
+      </c>
       <c r="Q24" s="3"/>
       <c r="R24" s="3"/>
       <c r="S24" s="3"/>
@@ -4496,7 +4525,9 @@
       <c r="O25" s="3">
         <v>5.7370000000000001</v>
       </c>
-      <c r="P25" s="3"/>
+      <c r="P25" s="3">
+        <v>8.1519999999999992</v>
+      </c>
       <c r="Q25" s="3"/>
       <c r="R25" s="3"/>
       <c r="S25" s="3"/>
@@ -4599,7 +4630,7 @@
         <v>134.85200000000003</v>
       </c>
       <c r="H26" s="3">
-        <f t="shared" ref="H26:O26" si="16">H23-H24+H25</f>
+        <f t="shared" ref="H26:P26" si="16">H23-H24+H25</f>
         <v>180.82800000000017</v>
       </c>
       <c r="I26" s="3">
@@ -4630,7 +4661,10 @@
         <f t="shared" si="16"/>
         <v>94.083999999999961</v>
       </c>
-      <c r="P26" s="3"/>
+      <c r="P26" s="3">
+        <f t="shared" si="16"/>
+        <v>260.29300000000018</v>
+      </c>
       <c r="Q26" s="3"/>
       <c r="R26" s="3"/>
       <c r="S26" s="3"/>
@@ -4757,7 +4791,9 @@
       <c r="O27" s="3">
         <v>25.965</v>
       </c>
-      <c r="P27" s="3"/>
+      <c r="P27" s="3">
+        <v>74.751999999999995</v>
+      </c>
       <c r="Q27" s="3"/>
       <c r="R27" s="3"/>
       <c r="S27" s="3"/>
@@ -4860,7 +4896,7 @@
         <v>115.05800000000004</v>
       </c>
       <c r="H28" s="3">
-        <f t="shared" ref="H28:O28" si="20">H26-H27</f>
+        <f t="shared" ref="H28:P28" si="20">H26-H27</f>
         <v>135.37900000000019</v>
       </c>
       <c r="I28" s="3">
@@ -4891,7 +4927,10 @@
         <f t="shared" si="20"/>
         <v>68.118999999999957</v>
       </c>
-      <c r="P28" s="3"/>
+      <c r="P28" s="3">
+        <f t="shared" si="20"/>
+        <v>185.54100000000017</v>
+      </c>
       <c r="Q28" s="3"/>
       <c r="R28" s="3"/>
       <c r="S28" s="3"/>
@@ -5018,7 +5057,9 @@
       <c r="O29" s="3">
         <v>0.98499999999999999</v>
       </c>
-      <c r="P29" s="3"/>
+      <c r="P29" s="3">
+        <v>1.819</v>
+      </c>
       <c r="Q29" s="3"/>
       <c r="R29" s="3"/>
       <c r="S29" s="3"/>
@@ -5121,7 +5162,7 @@
         <v>113.83000000000004</v>
       </c>
       <c r="H30" s="3">
-        <f t="shared" ref="H30:O30" si="23">H28-H29</f>
+        <f t="shared" ref="H30:P30" si="23">H28-H29</f>
         <v>133.16800000000018</v>
       </c>
       <c r="I30" s="3">
@@ -5152,7 +5193,10 @@
         <f t="shared" si="23"/>
         <v>67.133999999999958</v>
       </c>
-      <c r="P30" s="3"/>
+      <c r="P30" s="3">
+        <f t="shared" si="23"/>
+        <v>183.72200000000018</v>
+      </c>
       <c r="Q30" s="3"/>
       <c r="R30" s="3"/>
       <c r="S30" s="3"/>
@@ -5370,9 +5414,9 @@
         <f t="shared" si="25"/>
         <v>1.4928951055171331</v>
       </c>
-      <c r="P32" s="25" t="e">
+      <c r="P32" s="25">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>4.1977288824913783</v>
       </c>
       <c r="Q32" s="25"/>
       <c r="R32" s="25"/>
@@ -5500,7 +5544,9 @@
       <c r="O33" s="3">
         <v>44.969000000000001</v>
       </c>
-      <c r="P33" s="3"/>
+      <c r="P33" s="3">
+        <v>43.767000000000003</v>
+      </c>
       <c r="Q33" s="3"/>
       <c r="R33" s="3"/>
       <c r="S33" s="3"/>
@@ -5900,7 +5946,7 @@
       </c>
       <c r="P37" s="26">
         <f t="shared" si="29"/>
-        <v>-1</v>
+        <v>8.1432516471330318E-2</v>
       </c>
       <c r="Q37" s="26">
         <f t="shared" si="29"/>
@@ -6033,7 +6079,7 @@
       </c>
       <c r="P38" s="26">
         <f t="shared" si="32"/>
-        <v>-1</v>
+        <v>2.0083996759515887E-2</v>
       </c>
       <c r="Q38" s="26">
         <f t="shared" si="32"/>
@@ -6166,7 +6212,7 @@
       </c>
       <c r="P39" s="27">
         <f t="shared" si="34"/>
-        <v>-1</v>
+        <v>4.8097736148805303E-2</v>
       </c>
       <c r="Q39" s="27">
         <f t="shared" si="34"/>
@@ -6309,9 +6355,9 @@
         <f t="shared" si="37"/>
         <v>0.62845196849403984</v>
       </c>
-      <c r="P40" s="26" t="e">
+      <c r="P40" s="26">
         <f t="shared" si="37"/>
-        <v>#DIV/0!</v>
+        <v>0.71097167497309921</v>
       </c>
       <c r="Q40" s="26" t="e">
         <f t="shared" si="37"/>
@@ -6457,9 +6503,9 @@
         <f t="shared" si="41"/>
         <v>7.9722863907216668E-2</v>
       </c>
-      <c r="P41" s="26" t="e">
+      <c r="P41" s="26">
         <f t="shared" si="41"/>
-        <v>#DIV/0!</v>
+        <v>0.19949806148154769</v>
       </c>
       <c r="Q41" s="26" t="e">
         <f t="shared" si="41"/>
@@ -6605,9 +6651,9 @@
         <f t="shared" si="45"/>
         <v>6.0273598720081561E-2</v>
       </c>
-      <c r="P42" s="26" t="e">
+      <c r="P42" s="26">
         <f t="shared" si="45"/>
-        <v>#DIV/0!</v>
+        <v>0.14504112690644677</v>
       </c>
       <c r="Q42" s="26" t="e">
         <f t="shared" si="45"/>
@@ -6753,9 +6799,9 @@
         <f t="shared" si="49"/>
         <v>0.27597678670124581</v>
       </c>
-      <c r="P43" s="26" t="e">
+      <c r="P43" s="26">
         <f t="shared" si="49"/>
-        <v>#DIV/0!</v>
+        <v>0.28718405796544644</v>
       </c>
       <c r="Q43" s="26" t="e">
         <f t="shared" si="49"/>
@@ -25191,19 +25237,19 @@
     </row>
     <row r="69" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B69" s="73"/>
-      <c r="C69" s="78" t="s">
+      <c r="C69" s="79" t="s">
         <v>154</v>
       </c>
-      <c r="D69" s="78"/>
-      <c r="E69" s="78"/>
-      <c r="F69" s="78"/>
-      <c r="G69" s="78"/>
-      <c r="H69" s="78"/>
-      <c r="I69" s="78"/>
-      <c r="J69" s="79"/>
+      <c r="D69" s="79"/>
+      <c r="E69" s="79"/>
+      <c r="F69" s="79"/>
+      <c r="G69" s="79"/>
+      <c r="H69" s="79"/>
+      <c r="I69" s="79"/>
+      <c r="J69" s="80"/>
     </row>
     <row r="70" spans="1:22" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B70" s="80" t="s">
+      <c r="B70" s="81" t="s">
         <v>153</v>
       </c>
       <c r="C70" s="74"/>
@@ -25216,7 +25262,7 @@
       <c r="J70" s="75"/>
     </row>
     <row r="71" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B71" s="80"/>
+      <c r="B71" s="81"/>
       <c r="C71" s="76"/>
       <c r="D71" s="77"/>
       <c r="E71" s="77"/>
@@ -25227,7 +25273,7 @@
       <c r="J71" s="77"/>
     </row>
     <row r="72" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B72" s="80"/>
+      <c r="B72" s="81"/>
       <c r="C72" s="76"/>
       <c r="D72" s="77"/>
       <c r="E72" s="77"/>
@@ -25238,7 +25284,7 @@
       <c r="J72" s="77"/>
     </row>
     <row r="73" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B73" s="80"/>
+      <c r="B73" s="81"/>
       <c r="C73" s="76"/>
       <c r="D73" s="77"/>
       <c r="E73" s="77"/>
@@ -25249,7 +25295,7 @@
       <c r="J73" s="77"/>
     </row>
     <row r="74" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B74" s="80"/>
+      <c r="B74" s="81"/>
       <c r="C74" s="76"/>
       <c r="D74" s="77"/>
       <c r="E74" s="77"/>
@@ -25260,7 +25306,7 @@
       <c r="J74" s="77"/>
     </row>
     <row r="75" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B75" s="80"/>
+      <c r="B75" s="81"/>
       <c r="C75" s="76"/>
       <c r="D75" s="77"/>
       <c r="E75" s="77"/>
@@ -25271,7 +25317,7 @@
       <c r="J75" s="77"/>
     </row>
     <row r="76" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B76" s="80"/>
+      <c r="B76" s="81"/>
       <c r="C76" s="76"/>
       <c r="D76" s="77"/>
       <c r="E76" s="77"/>
@@ -25282,7 +25328,7 @@
       <c r="J76" s="77"/>
     </row>
     <row r="77" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B77" s="81"/>
+      <c r="B77" s="82"/>
       <c r="C77" s="76"/>
       <c r="D77" s="77"/>
       <c r="E77" s="77"/>
